--- a/Elec_case/dynLCI/dp-LCI_output/staticLCI_(p)GWP100/hydro_reservoir_CN-asRoW_US-asQC_staticLCI_threeGWP100.xlsx
+++ b/Elec_case/dynLCI/dp-LCI_output/staticLCI_(p)GWP100/hydro_reservoir_CN-asRoW_US-asQC_staticLCI_threeGWP100.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>gwp100</t>
   </si>
@@ -31,52 +31,34 @@
     <t>market for electricity, hydro, high voltage, US, SSP1-VLLO, 2030</t>
   </si>
   <si>
-    <t>market for electricity, hydro, high voltage, US, SSP1-VLLO, 2040</t>
-  </si>
-  <si>
     <t>market for electricity, hydro, high voltage, US, SSP1-VLLO, 2050</t>
   </si>
   <si>
     <t>market for electricity, hydro, high voltage, US, SSP2-M, 2030</t>
   </si>
   <si>
-    <t>market for electricity, hydro, high voltage, US, SSP2-M, 2040</t>
-  </si>
-  <si>
     <t>market for electricity, hydro, high voltage, US, SSP2-M, 2050</t>
   </si>
   <si>
     <t>market for electricity, hydro, high voltage, US, SSP5-H, 2030</t>
   </si>
   <si>
-    <t>market for electricity, hydro, high voltage, US, SSP5-H, 2040</t>
-  </si>
-  <si>
     <t>market for electricity, hydro, high voltage, US, SSP5-H, 2050</t>
   </si>
   <si>
     <t>market for electricity, hydro, high voltage, CN, SSP1-VLLO, 2030</t>
   </si>
   <si>
-    <t>market for electricity, hydro, high voltage, CN, SSP1-VLLO, 2040</t>
-  </si>
-  <si>
     <t>market for electricity, hydro, high voltage, CN, SSP1-VLLO, 2050</t>
   </si>
   <si>
     <t>market for electricity, hydro, high voltage, CN, SSP2-M, 2030</t>
   </si>
   <si>
-    <t>market for electricity, hydro, high voltage, CN, SSP2-M, 2040</t>
-  </si>
-  <si>
     <t>market for electricity, hydro, high voltage, CN, SSP2-M, 2050</t>
   </si>
   <si>
     <t>market for electricity, hydro, high voltage, CN, SSP5-H, 2030</t>
-  </si>
-  <si>
-    <t>market for electricity, hydro, high voltage, CN, SSP5-H, 2040</t>
   </si>
   <si>
     <t>market for electricity, hydro, high voltage, CN, SSP5-H, 2050</t>
@@ -437,7 +419,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -459,13 +441,13 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>0.01572073255865096</v>
+        <v>0.02721242387451541</v>
       </c>
       <c r="C2">
-        <v>0.01790949642495036</v>
+        <v>0.03042196831322258</v>
       </c>
       <c r="D2">
-        <v>0.01564961964995015</v>
+        <v>0.02656495719738081</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -473,13 +455,13 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>0.01502761782372176</v>
+        <v>0.02514929741373461</v>
       </c>
       <c r="C3">
-        <v>0.01698836339767998</v>
+        <v>0.02863289273248072</v>
       </c>
       <c r="D3">
-        <v>0.0150030713509994</v>
+        <v>0.02513386769317534</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -487,13 +469,13 @@
         <v>6</v>
       </c>
       <c r="B4">
-        <v>0.01365787490673016</v>
+        <v>0.02723748098703752</v>
       </c>
       <c r="C4">
-        <v>0.01553485203503237</v>
+        <v>0.02943832003411326</v>
       </c>
       <c r="D4">
-        <v>0.01364607085120712</v>
+        <v>0.02629898701856882</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -501,13 +483,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>0.01574582639656143</v>
+        <v>0.02695185531734251</v>
       </c>
       <c r="C5">
-        <v>0.017505039575353</v>
+        <v>0.02699384237972024</v>
       </c>
       <c r="D5">
-        <v>0.01564943666712725</v>
+        <v>0.02710500126124982</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -515,13 +497,13 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>0.0155618411093238</v>
+        <v>0.02729293993288842</v>
       </c>
       <c r="C6">
-        <v>0.01634293225101133</v>
+        <v>0.02853606009222924</v>
       </c>
       <c r="D6">
-        <v>0.01552186935319632</v>
+        <v>0.02591865003637973</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -529,13 +511,13 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>0.01546068005579618</v>
+        <v>0.02707391746799039</v>
       </c>
       <c r="C7">
-        <v>0.01538824904891281</v>
+        <v>0.02403169664360956</v>
       </c>
       <c r="D7">
-        <v>0.01546214441738055</v>
+        <v>0.02657936378642363</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -543,13 +525,13 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>0.0158012883553034</v>
+        <v>0.05052327410460816</v>
       </c>
       <c r="C8">
-        <v>0.01723632517846523</v>
+        <v>0.05726566305921448</v>
       </c>
       <c r="D8">
-        <v>0.01566623887066438</v>
+        <v>0.05002129201238376</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -557,13 +539,13 @@
         <v>11</v>
       </c>
       <c r="B9">
-        <v>0.01567793391131441</v>
+        <v>0.04743673221988098</v>
       </c>
       <c r="C9">
-        <v>0.01561262281642673</v>
+        <v>0.05397883122767464</v>
       </c>
       <c r="D9">
-        <v>0.01555922189833656</v>
+        <v>0.04740242110869345</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -571,13 +553,13 @@
         <v>12</v>
       </c>
       <c r="B10">
-        <v>0.01558249037485818</v>
+        <v>0.05062413242971225</v>
       </c>
       <c r="C10">
-        <v>0.01403629767258981</v>
+        <v>0.05584787589960262</v>
       </c>
       <c r="D10">
-        <v>0.01552817913234484</v>
+        <v>0.04991075917890589</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -585,13 +567,13 @@
         <v>13</v>
       </c>
       <c r="B11">
-        <v>0.05052321158674736</v>
+        <v>0.04984367713503863</v>
       </c>
       <c r="C11">
-        <v>0.05726559498803554</v>
+        <v>0.04970105204671182</v>
       </c>
       <c r="D11">
-        <v>0.05002123263004093</v>
+        <v>0.0499302471063752</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -599,13 +581,13 @@
         <v>14</v>
       </c>
       <c r="B12">
-        <v>0.04872434369718268</v>
+        <v>0.05076620089003005</v>
       </c>
       <c r="C12">
-        <v>0.05504079781454591</v>
+        <v>0.05473736040770803</v>
       </c>
       <c r="D12">
-        <v>0.04858731381974549</v>
+        <v>0.04973544251968624</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -613,97 +595,13 @@
         <v>15</v>
       </c>
       <c r="B13">
-        <v>0.04743668155690239</v>
+        <v>0.05038793265576484</v>
       </c>
       <c r="C13">
-        <v>0.05397877348149437</v>
+        <v>0.04519818412313044</v>
       </c>
       <c r="D13">
-        <v>0.04740237046169956</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14">
-        <v>0.0506240716426115</v>
-      </c>
-      <c r="C14">
-        <v>0.05584781277644521</v>
-      </c>
-      <c r="D14">
-        <v>0.04991070284626162</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15">
-        <v>0.05016714038066257</v>
-      </c>
-      <c r="C15">
-        <v>0.05256302093778377</v>
-      </c>
-      <c r="D15">
-        <v>0.04990881578455679</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16">
-        <v>0.04984364079505242</v>
-      </c>
-      <c r="C16">
-        <v>0.04970101534488699</v>
-      </c>
-      <c r="D16">
-        <v>0.04993021028670728</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17">
-        <v>0.05076614048384639</v>
-      </c>
-      <c r="C17">
-        <v>0.05473730101033961</v>
-      </c>
-      <c r="D17">
-        <v>0.04973538862760401</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18">
-        <v>0.05059495288758083</v>
-      </c>
-      <c r="C18">
-        <v>0.04985878762114201</v>
-      </c>
-      <c r="D18">
-        <v>0.04968123964054657</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19">
-        <v>0.05038788441940716</v>
-      </c>
-      <c r="C19">
-        <v>0.04519814216649301</v>
-      </c>
-      <c r="D19">
-        <v>0.05000597958617033</v>
+        <v>0.05000602597456853</v>
       </c>
     </row>
   </sheetData>
